--- a/output/testing_result_databaru/evaluation_testing_70_30.xlsx
+++ b/output/testing_result_databaru/evaluation_testing_70_30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,70 +429,80 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Jenis Rule</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Jenis Rule Label</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Support Training</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Confidence Training</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Lift Training</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Kategori Training</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Antecedent Support</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Consequent Support</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Lift</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Kategori Rule</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Count Antecedent</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Count Consequent</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Count Both</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Status Pengujian</t>
         </is>
@@ -509,50 +519,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>0.01301518438177874</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>0.5806451612903226</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>1.81681506349438</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.02698145025295109</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.3187183811129848</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>0.02192242833052277</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.8125</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>2.549272486772487</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>16</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>189</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>13</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -569,50 +589,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>0.01084598698481562</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>1.738310708898944</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.02698145025295109</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.3187183811129848</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.01686340640809443</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.625</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>1.960978835978836</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>16</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>189</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>10</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -629,50 +659,60 @@
           <t>operator_Oktavira</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>0.01084598698481562</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>0.4054054054054054</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>1.291879437040727</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.02192242833052277</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.2833052276559865</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>0.0118043844856661</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.5384615384615384</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>1.900641025641025</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>13</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>168</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -689,50 +729,60 @@
           <t>operator_Oktavira</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>0.01735357917570499</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>0.4444444444444445</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>1.416282642089094</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.04721753794266442</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.2833052276559865</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>0.02360876897133221</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.5</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>1.764880952380952</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>28</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>168</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>14</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -749,50 +799,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>0.01373825018076645</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>0.5135135135135135</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>1.080957669998766</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.01854974704890388</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>0.01349072512647555</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>1.562582345191041</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>11</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>276</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>8</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -809,50 +869,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>0.01663051337671728</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>0.4893617021276596</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>1.030117555620325</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.02698145025295109</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>0.01854974704890388</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.6875</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>1.477128623188406</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>16</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>276</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>11</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -869,50 +939,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>0.01012292118582791</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>0.5</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>1.56447963800905</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.03372681281618887</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.3187183811129848</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>0.01517706576728499</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.45</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>1.411904761904762</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>20</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>189</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>9</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -929,50 +1009,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>0.01156905278380333</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>0.4444444444444445</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>1.390648567119155</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.02360876897133221</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.3187183811129848</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>0.01011804384485666</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>1.344671201814059</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>14</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>189</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>6</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -989,50 +1079,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>0.01518438177874186</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>0.4883720930232557</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>1.028034405861739</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.03541315345699832</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>0.02192242833052277</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.6190476190476191</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>1.330055210489993</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>21</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>276</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>13</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1049,50 +1149,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>0.02024584237165582</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>0.6511627906976744</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>1.370712541148986</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>0.03372681281618887</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>0.02023608768971332</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.6</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>1.289130434782609</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
         <v>20</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>276</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>12</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1109,50 +1219,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>0.01012292118582791</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>2.167711598746082</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>0.01517706576728499</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.3456998313659359</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>0.006745362563237774</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.4444444444444444</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>1.285636856368564</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>205</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>4</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1169,50 +1289,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>0.01012292118582791</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>1.3395599833956</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>0.0118043844856661</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>0.006745362563237774</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>1.227743271221532</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
         <v>7</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>276</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>4</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1229,50 +1359,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>0.01446131597975416</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>0.5</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>1.052511415525114</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>0.02698145025295109</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>0.01517706576728499</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.5625</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>1.208559782608696</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
         <v>16</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>276</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>9</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1289,50 +1429,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>operator_waktu</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>0.0455531453362256</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>0.6237623762376238</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>1.31303404313034</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>0.05227655986509275</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>0.02866779089376054</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.5483870967741935</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>1.178237494156148</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
         <v>31</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>276</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>17</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1349,50 +1499,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
         <v>0.04844540853217643</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>0.5</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>1.052511415525114</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>0.1146711635750422</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>0.06239460370994941</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.5441176470588235</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>1.169064364876385</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
         <v>68</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>276</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>37</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1409,50 +1569,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
         <v>0.02241503976861894</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>0.5740740740740741</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>1.208439032639946</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>0.04721753794266442</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>0.02529510961214165</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.5357142857142857</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>1.151009316770186</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
         <v>28</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>276</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>15</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1469,50 +1639,60 @@
           <t>operator_Oktavira</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>0.01373825018076645</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>0.4523809523809524</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>1.44157340355497</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>0.04215851602023609</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.2833052276559865</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>0.01349072512647555</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.32</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>1.129523809523809</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>25</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>168</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>8</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -1529,50 +1709,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
         <v>0.01590744757772957</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>0.5238095238095238</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>1.784306826178748</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>0.03035413153456998</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.3456998313659359</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>0.0118043844856661</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.3888888888888889</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>1.124932249322493</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>18</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>205</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>7</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -1589,50 +1779,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
         <v>0.01590744757772957</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>0.5238095238095238</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>1.102631006740596</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>0.03035413153456998</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>0.01517706576728499</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.5</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>1.074275362318841</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
         <v>18</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>276</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>9</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1649,50 +1849,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>operator_waktu</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
         <v>0.1431670281995662</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>0.4876847290640395</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>1.026587489034348</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>0.3456998313659359</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>0.1669477234401349</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.4829268292682927</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>1.037592788971368</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M21" t="n">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
         <v>205</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>276</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>99</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1709,50 +1919,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
         <v>0.01373825018076645</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>0.6333333333333333</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>1.333181126331811</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="I22" t="n">
         <v>0.0387858347386172</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>0.01854974704890388</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.4782608695652174</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>1.027567737870195</v>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
         <v>23</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>276</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>11</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1769,50 +1989,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>operator_waktu</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
         <v>0.1540130151843818</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>0.4907834101382489</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>1.033110283441702</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>0.2833052276559865</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>0.1349072512647555</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>1.02311939268461</v>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M23" t="n">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
         <v>168</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>276</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>80</v>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1829,50 +2059,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
         <v>0.01156905278380333</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>0.5</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>1.052511415525114</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>0.02529510961214165</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>0.0118043844856661</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.4666666666666667</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>1.002657004830918</v>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
         <v>15</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>276</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>7</v>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1889,50 +2129,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
         <v>0.01518438177874186</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>0.5675675675675675</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>1.194742687893373</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>0.02192242833052277</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>0.01011804384485666</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.4615384615384616</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.9916387959866222</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>13</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>276</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>6</v>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -1949,50 +2199,60 @@
           <t>operator_Oktavira</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
         <v>0.01663051337671728</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>0.4181818181818182</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>1.332593213238375</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>0.01854974704890388</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.2833052276559865</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>0.00505902192242833</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.9626623376623376</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>11</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>168</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>3</v>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2009,50 +2269,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
         <v>0.01156905278380333</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>0.5517241379310345</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>1.7263223591824</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="I27" t="n">
         <v>0.02360876897133221</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.3187183811129848</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>0.006745362563237774</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.8964474678760392</v>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>14</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>189</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>4</v>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2069,50 +2339,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
         <v>0.02241503976861894</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>0.4769230769230769</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>1.62459264873058</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>0.04384485666104553</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.3456998313659359</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>0.01349072512647555</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.3076923076923077</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>0.8900562851782364</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>26</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>205</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>8</v>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2129,50 +2409,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
         <v>0.01301518438177874</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>0.5142857142857142</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>1.082583170254403</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>0.04553119730185497</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>0.01854974704890388</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.4074074074074074</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>0.8753354804079442</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>27</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>276</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2189,50 +2479,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
         <v>0.01084598698481562</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>1.892446633825944</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="I30" t="n">
         <v>0.01686340640809443</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.3456998313659359</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>0.00505902192242833</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.3</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.8678048780487805</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>10</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>205</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>3</v>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2249,50 +2549,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
         <v>0.01156905278380333</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>0.4102564102564102</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>1.283675600417682</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>0.01854974704890388</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.3187183811129848</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>0.00505902192242833</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.8556998556998556</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>11</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>189</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2309,50 +2619,60 @@
           <t>operator_Oktavira</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
         <v>0.02675343456254519</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>0.4065934065934065</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
         <v>1.295665164328759</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
         <v>0.08094435075885328</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.2833052276559865</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>0.01854974704890388</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.2291666666666667</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.8089037698412698</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>48</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>168</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>11</v>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2369,50 +2689,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
         <v>0.01084598698481562</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>0.4838709677419355</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>1.018559434379143</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>0.01349072512647555</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>0.00505902192242833</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.375</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.8057065217391305</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>8</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>276</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>3</v>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2429,50 +2759,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
         <v>0.01156905278380333</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>0.5517241379310345</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>1.161391906786333</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>0.02360876897133221</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>0.008431703204047217</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.3571428571428572</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.7673395445134575</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>14</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>276</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>5</v>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2489,50 +2829,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
         <v>0.01084598698481562</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>0.4054054054054054</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>1.268497003791121</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>0.02192242833052277</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.3187183811129848</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>0.00505902192242833</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.2307692307692308</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.724053724053724</v>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>13</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>189</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>3</v>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2549,50 +2899,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
         <v>0.01373825018076645</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>0.6129032258064516</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>1.290175283546914</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>0.02023608768971332</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>0.006745362563237774</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.716183574879227</v>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>12</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>276</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>4</v>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2609,50 +2969,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
         <v>0.01446131597975416</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>0.5263157894736842</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>1.107906753184331</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>0.03372681281618887</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.4654300168634064</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>0.006745362563237774</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.2</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.4297101449275363</v>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>20</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>276</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>4</v>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2669,50 +3039,60 @@
           <t>operator_Oktavira</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
         <v>0.01156905278380333</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>0.4102564102564102</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>1.307337823466856</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
         <v>0.01854974704890388</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.2833052276559865</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>11</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>168</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0</v>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
